--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:25</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -895,7 +895,7 @@
         <v>-0.42</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>-0.12</v>
@@ -918,7 +918,7 @@
         <v>-0.16</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.47</v>
@@ -941,7 +941,7 @@
         <v>-0.34</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>0.01</v>
@@ -964,10 +964,10 @@
         <v>-0.15</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="20">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:15</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -524,7 +524,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="31.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="33.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="14.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="10.71" hidden="0" customWidth="1"/>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_i_ingr_a_2021_la_araucania.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
